--- a/entertainment_forms/012_performer_and_promoter_agreement--entertainment_forms.xlsx
+++ b/entertainment_forms/012_performer_and_promoter_agreement--entertainment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'concert',_'value':_'concert'}</t>
+          <t>concert</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Concert', 'value': 'concert'}</t>
+          <t>Concert</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'show',_'value':_'show'}</t>
+          <t>show</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Show', 'value': 'show'}</t>
+          <t>Show</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'meet',_'value':_'meet'}</t>
+          <t>meet</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Meet', 'value': 'meet'}</t>
+          <t>Meet</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'cash',_'value':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Cash', 'value': 'cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'check',_'value':_'check'}</t>
+          <t>check</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Check', 'value': 'check'}</t>
+          <t>Check</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'wire_transfer',_'value':_'wire-transfer'}</t>
+          <t>wire_transfer</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Wire Transfer', 'value': 'wire-transfer'}</t>
+          <t>Wire Transfer</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'upcoming',_'value':_'upcoming'}</t>
+          <t>upcoming</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Upcoming', 'value': 'upcoming'}</t>
+          <t>Upcoming</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'past',_'value':_'past'}</t>
+          <t>past</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Past', 'value': 'past'}</t>
+          <t>Past</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'present',_'value':_'present'}</t>
+          <t>present</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Present', 'value': 'present'}</t>
+          <t>Present</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'active',_'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Active', 'value': 'active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'inactive',_'value':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Inactive', 'value': 'inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
